--- a/ResourcesTH/ExcelTemplateForOutletCreation.xlsx
+++ b/ResourcesTH/ExcelTemplateForOutletCreation.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="137">
   <si>
     <t>Outlet Code</t>
   </si>
@@ -406,6 +406,30 @@
   </si>
   <si>
     <t>03095194200</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL3F5C5</t>
+  </si>
+  <si>
+    <t>03147256900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLAB2F1</t>
+  </si>
+  <si>
+    <t>03149187400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLC21E5</t>
+  </si>
+  <si>
+    <t>03947926500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL0C757</t>
+  </si>
+  <si>
+    <t>03949603700</t>
   </si>
 </sst>
 </file>
@@ -1031,7 +1055,7 @@
     <row r="2" spans="1:73" ht="18.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>73</v>
@@ -1073,7 +1097,7 @@
         <v>12.12</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>24.44553759225542</v>
+        <v>24.39981013862835</v>
       </c>
       <c r="R2" s="1" t="s">
         <v>82</v>
@@ -1166,7 +1190,7 @@
         <v>78</v>
       </c>
       <c r="AY2" s="1" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="AZ2" s="1" t="s">
         <v>78</v>
@@ -1238,7 +1262,7 @@
     <row r="3" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>101</v>
@@ -1280,7 +1304,7 @@
         <v>12.12</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>24.682774627369987</v>
+        <v>24.670303541347007</v>
       </c>
       <c r="R3" s="1" t="s">
         <v>82</v>
@@ -1373,7 +1397,7 @@
         <v>78</v>
       </c>
       <c r="AY3" s="1" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="AZ3" s="1" t="s">
         <v>78</v>
